--- a/Result/profitability/2891.xlsx
+++ b/Result/profitability/2891.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM96"/>
+  <dimension ref="A1:AM97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>0.95375</v>
+        <v>0.91375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.88625</v>
+        <v>0.8975000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -877,7 +877,7 @@
         <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0.89625</v>
+        <v>0.86625</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,7 +988,7 @@
         <v>0.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0.875</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1099,11 +1099,11 @@
         <v>0.77</v>
       </c>
       <c r="M6" t="n">
-        <v>0.87625</v>
+        <v>0.81375</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>-0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6224999999999999</v>
+        <v>0.5925</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1337,7 +1337,7 @@
         <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5975</v>
+        <v>0.5475</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1698,7 +1698,7 @@
         <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="N11" t="n">
         <v>62.49625</v>
@@ -2182,7 +2182,7 @@
         <v>0.27</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6537499999999999</v>
+        <v>0.6537500000000001</v>
       </c>
       <c r="N15" t="n">
         <v>62.5875</v>
@@ -2303,7 +2303,7 @@
         <v>0.06</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5587500000000001</v>
+        <v>0.55875</v>
       </c>
       <c r="N16" t="n">
         <v>58.24125</v>
@@ -2545,7 +2545,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="N18" t="n">
         <v>46.25</v>
@@ -11030,6 +11030,113 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>58738</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>20917</v>
+      </c>
+      <c r="K97" t="n">
+        <v>16434</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.97875</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="X97" t="n">
+        <v>-0.3389830508474576</v>
+      </c>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.02631578947368429</v>
+      </c>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK97" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
